--- a/ARM Functions/plan for editing mega stones.xlsx
+++ b/ARM Functions/plan for editing mega stones.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B83809-4A4A-4311-9DBF-8D40D9BC5A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD5F0DF-D749-4C21-9DE5-54073356DAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12600" yWindow="4569" windowWidth="24686" windowHeight="12831" xr2:uid="{CE65C796-4B30-4162-9983-C38F0EBC8250}"/>
+    <workbookView xWindow="-31817" yWindow="2374" windowWidth="24686" windowHeight="12497" xr2:uid="{CE65C796-4B30-4162-9983-C38F0EBC8250}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>Delibird</t>
   </si>
@@ -47,57 +47,21 @@
     <t>Swellow</t>
   </si>
   <si>
-    <t>Gumshoos</t>
-  </si>
-  <si>
     <t>Swellowite</t>
   </si>
   <si>
-    <t>Gumshoosinite</t>
-  </si>
-  <si>
-    <t>magic Guard</t>
-  </si>
-  <si>
-    <t>Meowsticite</t>
-  </si>
-  <si>
-    <t>Meowstic</t>
-  </si>
-  <si>
-    <t>Crabominite</t>
-  </si>
-  <si>
-    <t>Crabominable</t>
-  </si>
-  <si>
     <t>Golisopite</t>
   </si>
   <si>
     <t>Golisopod</t>
   </si>
   <si>
-    <t>Raichunite X</t>
-  </si>
-  <si>
-    <t>Raichu</t>
-  </si>
-  <si>
-    <t>Raichunite Y</t>
-  </si>
-  <si>
     <t>Absolite Z</t>
   </si>
   <si>
     <t>Absol</t>
   </si>
   <si>
-    <t>Staraptite</t>
-  </si>
-  <si>
-    <t>Staraptor</t>
-  </si>
-  <si>
     <t>Garchompite Z</t>
   </si>
   <si>
@@ -110,90 +74,24 @@
     <t>Zeraorite</t>
   </si>
   <si>
-    <t>Drampa</t>
-  </si>
-  <si>
-    <t>Drampanite</t>
-  </si>
-  <si>
     <t>Zygarde</t>
   </si>
   <si>
     <t>Zygardite</t>
   </si>
   <si>
-    <t>Hawlucha</t>
-  </si>
-  <si>
-    <t>Hawluchanite</t>
-  </si>
-  <si>
-    <t>Dragalge</t>
-  </si>
-  <si>
-    <t>Dragalgite</t>
-  </si>
-  <si>
-    <t>Barbaracle</t>
-  </si>
-  <si>
-    <t>Barbaracite</t>
-  </si>
-  <si>
-    <t>Malamar</t>
-  </si>
-  <si>
-    <t>Malamarite</t>
-  </si>
-  <si>
     <t>Floettite</t>
   </si>
   <si>
     <t>Eternal Floette</t>
   </si>
   <si>
-    <t>Pyroar</t>
-  </si>
-  <si>
-    <t>Pyroarite</t>
-  </si>
-  <si>
     <t>Greninja</t>
   </si>
   <si>
     <t>Greninjite</t>
   </si>
   <si>
-    <t>Eelektross</t>
-  </si>
-  <si>
-    <t>Eelektrossite</t>
-  </si>
-  <si>
-    <t>Scrafty</t>
-  </si>
-  <si>
-    <t>Scraftinite</t>
-  </si>
-  <si>
-    <t>Scolipede</t>
-  </si>
-  <si>
-    <t>Scolipite</t>
-  </si>
-  <si>
-    <t>Excadrill</t>
-  </si>
-  <si>
-    <t>Excadrite</t>
-  </si>
-  <si>
-    <t>Emboar</t>
-  </si>
-  <si>
-    <t>Emboarite</t>
-  </si>
-  <si>
     <t>Darkrai</t>
   </si>
   <si>
@@ -206,24 +104,12 @@
     <t>Heatranite</t>
   </si>
   <si>
-    <t>Starmie</t>
-  </si>
-  <si>
-    <t>Starminite</t>
-  </si>
-  <si>
     <t>remove, make regular forme(?)</t>
   </si>
   <si>
-    <t>Ultra</t>
-  </si>
-  <si>
     <t>half damage when partner is Pikachu</t>
   </si>
   <si>
-    <t>Illuminate, 75/110/107/134/129/183</t>
-  </si>
-  <si>
     <t>Persian</t>
   </si>
   <si>
@@ -260,25 +146,16 @@
     <t>Porygonzinite</t>
   </si>
   <si>
-    <t>punch moves +20% | 129/175/134/82/118/118</t>
-  </si>
-  <si>
     <t>possible</t>
   </si>
   <si>
-    <t>Same Protect-piercing Golurkite got 141/176/107/69/89/135</t>
-  </si>
-  <si>
-    <t>Levitate | 119/108/139/206/147/55</t>
-  </si>
-  <si>
-    <t>Flying press animation becomes Dragon Ascent (regular), Dazzling | 109/160/117/104/109/165</t>
-  </si>
-  <si>
-    <t>Add Dragon, Magic Guard | 151/165/135/133/135/102</t>
-  </si>
-  <si>
-    <t>Oblivious 121/90/113/175/124/155</t>
+    <t>Raticanite</t>
+  </si>
+  <si>
+    <t>Shayminite</t>
+  </si>
+  <si>
+    <t>Kyuremite</t>
   </si>
 </sst>
 </file>
@@ -662,381 +539,285 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36BC728F-8D66-42E3-8CFD-919A7CAF0E77}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.46484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="15.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B4" s="3"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" s="3"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <f>D4+1</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>73</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B6" s="3"/>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D23" si="0">D5+1</f>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="31.75" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>75</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B8" s="3"/>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>78</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B9" s="3"/>
       <c r="C9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="31.75" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>77</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B11" s="3"/>
       <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
         <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B12" s="3"/>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="1">
-        <v>140</v>
-      </c>
-      <c r="B13" s="3">
-        <f>A13*225/189</f>
-        <v>166.66666666666666</v>
-      </c>
-      <c r="C13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="1" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="1" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" t="s">
-        <v>65</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:C41">
-    <sortCondition ref="A14:A41"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>